--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -24,8 +24,11 @@
     <sheet name="SERIES" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="CLUBS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="META" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -33,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +51,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,12 +96,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12377,7 +12395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12421,6 +12439,93 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2001_02_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2001_02_0030 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2001_02_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0021</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2001_02_0021 'Baráž o Extraligu' (L15, parent=NODE_S2001_02_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0028</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2001_02_0028 'Baráž o I.ligu' (L25, parent=NODE_S2001_02_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0047</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2001_02_0047 'O postup do I.ligy' (L25, parent=NODE_S2001_02_0041) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -16161,8 +16266,6 @@
         </is>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -16242,7 +16345,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
@@ -35009,6 +35111,193 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0029</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0030</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0030 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0031</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0021</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2001_02_0021 'Baráž o Extraligu' (L15, parent=NODE_S2001_02_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0028</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2001_02_0028 'Baráž o I.ligu' (L25, parent=NODE_S2001_02_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0047</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2001_02_0047 'O postup do I.ligy' (L25, parent=NODE_S2001_02_0041) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6287,11 +6287,7 @@
           <t>CLUB_S2001_02_0265</t>
         </is>
       </c>
-      <c r="R57" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0003</t>
-        </is>
-      </c>
+      <c r="R57" s="3" t="n"/>
       <c r="S57" s="3" t="n"/>
       <c r="T57" s="3" t="n"/>
       <c r="U57" s="3" t="n"/>
@@ -6336,11 +6332,7 @@
           <t>CLUB_S2001_02_0266</t>
         </is>
       </c>
-      <c r="R58" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0003</t>
-        </is>
-      </c>
+      <c r="R58" s="3" t="n"/>
       <c r="S58" s="3" t="n"/>
       <c r="T58" s="3" t="n"/>
       <c r="U58" s="3" t="n"/>
@@ -6430,11 +6422,7 @@
           <t>CLUB_S2001_02_0268</t>
         </is>
       </c>
-      <c r="R60" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0003</t>
-        </is>
-      </c>
+      <c r="R60" s="3" t="n"/>
       <c r="S60" s="3" t="n"/>
       <c r="T60" s="3" t="n"/>
       <c r="U60" s="3" t="n"/>
@@ -6847,11 +6835,7 @@
           <t>CLUB_S2001_02_0277</t>
         </is>
       </c>
-      <c r="R69" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0003</t>
-        </is>
-      </c>
+      <c r="R69" s="3" t="n"/>
       <c r="S69" s="3" t="n"/>
       <c r="T69" s="3" t="n"/>
       <c r="U69" s="3" t="n"/>
@@ -12395,7 +12379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12445,7 +12429,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2001_02_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -12457,7 +12441,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2001_02_0030 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -12469,7 +12453,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2001_02_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12479,14 +12463,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S2001_02_0021</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2001_02_0021 'Baráž o Extraligu' (L15, parent=NODE_S2001_02_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12496,14 +12475,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S2001_02_0028</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2001_02_0028 'Baráž o I.ligu' (L25, parent=NODE_S2001_02_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12513,17 +12487,644 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S2001_02_0047</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2001_02_0047 'O postup do I.ligy' (L25, parent=NODE_S2001_02_0041) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0042 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Earth Force Příbram' → 'Příbram' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Louny' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ústí nad Labem' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0030</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0031</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0032</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0033</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -16266,6 +16867,8 @@
         </is>
       </c>
     </row>
+    <row r="90"/>
+    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -16296,6 +16899,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0001</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -16308,6 +16916,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0003</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -16320,6 +16933,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0003</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -16332,6 +16950,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0041</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -16345,6 +16968,7 @@
         </is>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
@@ -19895,12 +20519,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -20063,12 +20687,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -20315,12 +20939,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -20399,12 +21023,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -20441,12 +21065,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -20777,12 +21401,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -21350,12 +21974,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -21602,12 +22226,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Slaný = HK Lev Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). '(II)' = druzstvo II. city Slaný.</t>
+          <t>Slaný = HK Lev Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). '(II)' = druzstvo II. city Slaný. || TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>HK Lev Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -21859,12 +22483,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -21943,12 +22567,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -21985,12 +22609,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk.</t>
+          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk. || TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
@@ -22027,12 +22651,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -22116,12 +22740,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -22793,12 +23417,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -23213,12 +23837,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Benešov = HC VHS Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **VHS** = Vodohospodářské stavby. city Benešov.</t>
+          <t>Benešov = HC VHS Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **VHS** = Vodohospodářské stavby. city Benešov. || TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>VHS HC Benešov</t>
+          <t>Benešov</t>
         </is>
       </c>
     </row>
@@ -23606,12 +24230,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Příbram = HC Earth Force Příbram (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni anglicky nazev. city Příbram.</t>
+          <t>Příbram = HC Earth Force Příbram (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni anglicky nazev. city Příbram. || TBD: city 'Earth Force Příbram' → 'Příbram' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Earth Force Příbram</t>
+          <t>Příbram</t>
         </is>
       </c>
     </row>
@@ -24884,12 +25508,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -25225,12 +25849,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -25356,12 +25980,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -25440,12 +26064,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -25482,12 +26106,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -25576,12 +26200,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -25717,12 +26341,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -25937,12 +26561,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -26120,12 +26744,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -26167,12 +26791,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -26214,12 +26838,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -28917,12 +29541,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Stadion Litoměřice</t>
         </is>
       </c>
     </row>
@@ -28959,12 +29583,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -29085,12 +29709,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -29127,12 +29751,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny.</t>
+          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny. || TBD: city 'Louny' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Louny</t>
+          <t>Stadion Litoměřice</t>
         </is>
       </c>
     </row>
@@ -29169,12 +29793,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -29552,12 +30176,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -29636,12 +30260,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -30541,14 +31165,9 @@
           <t>skupina A</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0003</t>
-        </is>
-      </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Tesla Pardubice = Dynamo Pardubice (Wiki D42 - registr ustavy 04/2026). Chain LTC Pardubice -&gt; Tesla -&gt; Dynamo. city Pardubice.</t>
+          <t>Tesla Pardubice = Dynamo Pardubice (Wiki D42 - registr ustavy 04/2026). Chain LTC Pardubice -&gt; Tesla -&gt; Dynamo. city Pardubice. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -30588,14 +31207,9 @@
           <t>skupina A</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0003</t>
-        </is>
-      </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Tesla Pardubice = Dynamo Pardubice (Wiki D42 - registr ustavy 04/2026). Chain LTC Pardubice -&gt; Tesla -&gt; Dynamo. city Pardubice.</t>
+          <t>Tesla Pardubice = Dynamo Pardubice (Wiki D42 - registr ustavy 04/2026). Chain LTC Pardubice -&gt; Tesla -&gt; Dynamo. city Pardubice. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -30677,14 +31291,9 @@
           <t>skupina A</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0003</t>
-        </is>
-      </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Tesla Pardubice = Dynamo Pardubice (Wiki D42 - registr ustavy 04/2026). Chain LTC Pardubice -&gt; Tesla -&gt; Dynamo. city Pardubice.</t>
+          <t>Tesla Pardubice = Dynamo Pardubice (Wiki D42 - registr ustavy 04/2026). Chain LTC Pardubice -&gt; Tesla -&gt; Dynamo. city Pardubice. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -31070,14 +31679,9 @@
           <t>skupina B</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0003</t>
-        </is>
-      </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Tesla Pardubice = Dynamo Pardubice (Wiki D42 - registr ustavy 04/2026). Chain LTC Pardubice -&gt; Tesla -&gt; Dynamo. city Pardubice.</t>
+          <t>Tesla Pardubice = Dynamo Pardubice (Wiki D42 - registr ustavy 04/2026). Chain LTC Pardubice -&gt; Tesla -&gt; Dynamo. city Pardubice. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -31527,12 +32131,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Ústí nad Labem' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Orlicí</t>
         </is>
       </c>
     </row>
@@ -33221,12 +33825,12 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -33550,12 +34154,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -33785,12 +34389,12 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>Velké Meziříčí = HC Florida Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. Post-revolucni nazev. city Velké Meziříčí.</t>
+          <t>Velké Meziříčí = HC Florida Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. Post-revolucni nazev. city Velké Meziříčí. || TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>Florida Velké Meziříčí</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
@@ -34430,12 +35034,12 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>Kravaře = HC Buly Centrum Kravaře (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Kravaře.</t>
+          <t>Kravaře = HC Buly Centrum Kravaře (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Kravaře. || TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>Buly Centrum Kravaře</t>
+          <t>Kravaře</t>
         </is>
       </c>
     </row>
@@ -35121,11 +35725,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -35170,21 +35774,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0029</t>
+          <t>CLUB_S2001_02_0008</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -35192,21 +35794,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0030</t>
+          <t>CLUB_S2001_02_0012</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0030 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -35214,21 +35814,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0031</t>
+          <t>CLUB_S2001_02_0018</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -35236,21 +35834,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S2001_02_0021</t>
+          <t>CLUB_S2001_02_0020</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2001_02_0021 'Baráž o Extraligu' (L15, parent=NODE_S2001_02_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -35258,21 +35854,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S2001_02_0028</t>
+          <t>CLUB_S2001_02_0021</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2001_02_0028 'Baráž o I.ligu' (L25, parent=NODE_S2001_02_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -35280,24 +35874,1042 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S2001_02_0047</t>
+          <t>CLUB_S2001_02_0029</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2001_02_0047 'O postup do I.ligy' (L25, parent=NODE_S2001_02_0041) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0043</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0042 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0049</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0056</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0063</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0065</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0066</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0067</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0069</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0086</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0096</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0105</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Earth Force Příbram' → 'Příbram' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0135</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0135</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0143</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0146</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0146</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0148</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0149</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0151</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0154</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0159</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0163</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0164</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0165</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0211</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0225</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0226</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0227</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0230</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0231</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0231</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Louny' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0232</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0236</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0242</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0244</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0247</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0265</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0266</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0268</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0277</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0286</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0287</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0287</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ústí nad Labem' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0326</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0333</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0338</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CLUB_S2001_02_0355</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0030</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0031</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0032</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0033</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48819,6 +50431,11 @@
           <t>CLUB_S2000_01_0116</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr">
         <is>
           <t>TR_S2001_02_00130</t>
@@ -53843,6 +55460,11 @@
           <t>CLUB_S2000_01_0026</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>TR_S2001_02_00146</t>
@@ -53888,6 +55510,11 @@
       <c r="R12" t="inlineStr">
         <is>
           <t>CLUB_S2000_01_0227</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>zanik</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -53978,6 +55605,11 @@
           <t>CLUB_S2000_01_0026</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>TR_S2001_02_00148</t>
@@ -54064,6 +55696,11 @@
       <c r="R16" t="inlineStr">
         <is>
           <t>CLUB_S2000_01_0233</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>zanik</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12379,7 +12379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12441,7 +12441,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -12453,7 +12453,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12465,7 +12465,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0042 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12477,7 +12477,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12489,7 +12489,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -12501,7 +12501,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0042 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12513,7 +12513,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12525,7 +12525,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12537,7 +12537,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12549,7 +12549,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12561,7 +12561,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Earth Force Příbram' → 'Příbram' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -12573,7 +12573,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -12585,7 +12585,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -12597,7 +12597,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -12609,7 +12609,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12621,7 +12621,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Earth Force Příbram' → 'Příbram' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12633,7 +12633,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -12645,7 +12645,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -12657,7 +12657,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -12669,7 +12669,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -12681,7 +12681,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -12693,7 +12693,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -12705,7 +12705,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -12717,7 +12717,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -12729,7 +12729,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -12741,7 +12741,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -12753,7 +12753,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -12765,7 +12765,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -12777,7 +12777,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -12789,7 +12789,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -12801,7 +12801,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -12813,7 +12813,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -12825,7 +12825,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -12837,7 +12837,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -12849,7 +12849,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -12859,9 +12859,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0030</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Louny' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -12871,9 +12876,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0031</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -12883,9 +12893,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0032</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -12895,236 +12910,17 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0033</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ústí nad Labem' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NODE_S2001_02_0030</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NODE_S2001_02_0031</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>NODE_S2001_02_0032</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>NODE_S2001_02_0033</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -13141,7 +12937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13200,6 +12996,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13242,6 +13043,11 @@
           <t>14 týmů (5 stat sloupců): základ + QF/SF/finále + baráž. Mistr: HC Sparta Praha.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13289,6 +13095,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13331,6 +13142,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13373,6 +13189,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13415,6 +13236,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13457,6 +13283,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13499,6 +13330,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13541,6 +13377,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13583,6 +13424,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13625,6 +13471,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13667,6 +13518,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13709,6 +13565,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13751,6 +13612,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13793,6 +13659,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13835,6 +13706,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13877,6 +13753,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13919,6 +13800,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13961,6 +13847,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14003,6 +13894,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14045,6 +13941,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14087,6 +13988,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14129,6 +14035,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14171,6 +14082,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14213,6 +14129,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14255,6 +14176,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14297,6 +14223,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14339,6 +14270,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14428,6 +14364,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14598,6 +14539,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0032</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -14724,6 +14670,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0035</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -14892,6 +14843,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0036</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14934,6 +14890,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0037</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14976,6 +14937,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0038</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -15018,6 +14984,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0039</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -15060,6 +15031,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0040</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -15102,6 +15078,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0041</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -15144,6 +15125,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0042</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -15186,6 +15172,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0043</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -15228,6 +15219,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0044</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -15354,6 +15350,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0045</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15396,6 +15397,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0046</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15522,6 +15528,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0048</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -15564,6 +15575,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0049</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -15606,6 +15622,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0050</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -15648,6 +15669,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0051</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -15690,6 +15716,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0052</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -15732,6 +15763,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0053</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -15774,6 +15810,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0054</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -15816,6 +15857,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0055</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -15858,6 +15904,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0056</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -15900,6 +15951,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0060</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -15942,6 +15998,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0061</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -15984,6 +16045,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0062</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -16068,6 +16134,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0064</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -16110,6 +16181,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0065</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -16152,6 +16228,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0066</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -16194,6 +16275,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0067</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -16614,6 +16700,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0072</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -16656,6 +16747,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0073</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -16698,6 +16794,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0085</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16738,6 +16839,11 @@
       <c r="K86" t="inlineStr">
         <is>
           <t>Kontejner L50</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0086</t>
         </is>
       </c>
     </row>
@@ -16887,6 +16993,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -16904,6 +17015,11 @@
           <t>NODE_S2001_02_0001</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -16921,6 +17037,11 @@
           <t>NODE_S2001_02_0003</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -16938,6 +17059,11 @@
           <t>NODE_S2001_02_0003</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -16955,6 +17081,11 @@
           <t>NODE_S2001_02_0041</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -16965,6 +17096,11 @@
       <c r="B98" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -20687,12 +20823,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -21065,12 +21201,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -21401,12 +21537,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -22483,12 +22619,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -23417,12 +23553,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -25508,12 +25644,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -25849,12 +25985,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -25980,12 +26116,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -26064,12 +26200,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -26106,12 +26242,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -26200,12 +26336,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -26341,12 +26477,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -26561,12 +26697,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -29541,12 +29677,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Stadion Litoměřice</t>
+          <t>Teplice</t>
         </is>
       </c>
     </row>
@@ -29751,12 +29887,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny. || TBD: city 'Louny' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny.</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Stadion Litoměřice</t>
+          <t>Louny</t>
         </is>
       </c>
     </row>
@@ -30176,12 +30312,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Nový Bydžov</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -32131,12 +32267,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Ústí nad Labem' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Ústí nad Orlicí</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -35725,7 +35861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -35799,12 +35935,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0012</t>
+          <t>CLUB_S2001_02_0018</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35819,12 +35955,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0018</t>
+          <t>CLUB_S2001_02_0020</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35839,12 +35975,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0020</t>
+          <t>CLUB_S2001_02_0043</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0042 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -35859,12 +35995,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0021</t>
+          <t>CLUB_S2001_02_0049</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35879,12 +36015,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0029</t>
+          <t>CLUB_S2001_02_0056</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35899,12 +36035,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0043</t>
+          <t>CLUB_S2001_02_0065</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0042 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35919,12 +36055,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0049</t>
+          <t>CLUB_S2001_02_0066</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35939,12 +36075,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0056</t>
+          <t>CLUB_S2001_02_0067</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35959,12 +36095,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0063</t>
+          <t>CLUB_S2001_02_0069</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35979,12 +36115,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0065</t>
+          <t>CLUB_S2001_02_0096</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -35999,12 +36135,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0066</t>
+          <t>CLUB_S2001_02_0105</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Earth Force Příbram' → 'Příbram' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36019,12 +36155,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0067</t>
+          <t>CLUB_S2001_02_0135</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36039,12 +36175,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0069</t>
+          <t>CLUB_S2001_02_0146</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36059,12 +36195,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0086</t>
+          <t>CLUB_S2001_02_0163</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36079,12 +36215,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0096</t>
+          <t>CLUB_S2001_02_0164</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36099,12 +36235,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0105</t>
+          <t>CLUB_S2001_02_0165</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Earth Force Příbram' → 'Příbram' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36119,12 +36255,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0135</t>
+          <t>CLUB_S2001_02_0211</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -36139,12 +36275,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0135</t>
+          <t>CLUB_S2001_02_0225</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -36159,12 +36295,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0143</t>
+          <t>CLUB_S2001_02_0227</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36179,12 +36315,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0146</t>
+          <t>CLUB_S2001_02_0230</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36199,12 +36335,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0146</t>
+          <t>CLUB_S2001_02_0231</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -36219,12 +36355,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0148</t>
+          <t>CLUB_S2001_02_0232</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36239,12 +36375,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0149</t>
+          <t>CLUB_S2001_02_0236</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -36259,12 +36395,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0151</t>
+          <t>CLUB_S2001_02_0244</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36279,12 +36415,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0154</t>
+          <t>CLUB_S2001_02_0247</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -36299,12 +36435,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0159</t>
+          <t>CLUB_S2001_02_0265</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36319,12 +36455,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0163</t>
+          <t>CLUB_S2001_02_0266</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36339,12 +36475,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0164</t>
+          <t>CLUB_S2001_02_0268</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36359,12 +36495,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0165</t>
+          <t>CLUB_S2001_02_0277</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36379,12 +36515,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0211</t>
+          <t>CLUB_S2001_02_0286</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -36399,12 +36535,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0225</t>
+          <t>CLUB_S2001_02_0287</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36419,12 +36555,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0226</t>
+          <t>CLUB_S2001_02_0326</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36439,12 +36575,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0227</t>
+          <t>CLUB_S2001_02_0333</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36459,12 +36595,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0230</t>
+          <t>CLUB_S2001_02_0338</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36479,12 +36615,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0231</t>
+          <t>CLUB_S2001_02_0355</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36494,17 +36630,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0231</t>
+          <t>NODE_S2001_02_0030</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Louny' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
         </is>
       </c>
     </row>
@@ -36514,17 +36650,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0232</t>
+          <t>NODE_S2001_02_0031</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
         </is>
       </c>
     </row>
@@ -36534,17 +36670,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0236</t>
+          <t>NODE_S2001_02_0032</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
     </row>
@@ -36554,362 +36690,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0242</t>
+          <t>NODE_S2001_02_0033</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0244</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0247</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0265</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0266</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0268</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0277</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0286</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0287</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0287</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Ústí nad Labem' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0326</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0333</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0338</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0355</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>NODE_S2001_02_0030</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>NODE_S2001_02_0031</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>NODE_S2001_02_0032</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>NODE_S2001_02_0033</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F58"/>
+  <autoFilter ref="A1:F41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12379,7 +12379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12427,33 +12427,43 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KVAL</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] TJ Bohemians Praha ze soutěže před začátkem odstoupila. (club_id: CLUB_S2001_02_0040)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] HC Mladá Boleslav "B" po skončení soutěže ukončila činnost (club_id: CLUB_S2001_02_0086)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12465,7 +12475,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0042 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12477,7 +12487,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12489,7 +12499,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: extrahováno z block_name: 'TJ Bohemians Praha ze soutěže před začátkem odstoupila.' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -12501,7 +12511,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0042 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12513,7 +12523,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12525,7 +12535,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12537,7 +12547,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12549,7 +12559,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12561,7 +12571,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Earth Force Příbram' → 'Příbram' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -12573,7 +12583,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -12585,7 +12595,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: extrahováno z block_name: 'HC Mladá Boleslav "B" po skončení soutěže ukončila činnost' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -12597,7 +12607,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -12609,7 +12619,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Earth Force Příbram' → 'Příbram' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12621,7 +12631,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12633,7 +12643,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -12645,7 +12655,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -12657,7 +12667,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -12669,7 +12679,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -12681,7 +12691,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -12693,7 +12703,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -12705,7 +12715,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -12717,7 +12727,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -12729,7 +12739,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -12741,7 +12751,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -12753,7 +12763,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -12765,7 +12775,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -12777,7 +12787,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -12789,7 +12799,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -12801,7 +12811,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -12813,7 +12823,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -12825,7 +12835,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -12837,7 +12847,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -12849,78 +12859,126 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>NODE_S2001_02_0030</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>NODE_S2001_02_0031</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>NODE_S2001_02_0032</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>NODE_S2001_02_0033</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -21774,7 +21832,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha. || TBD: extrahováno z block_name: 'TJ Bohemians Praha ze soutěže před začátkem odstoupila.' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -23553,7 +23611,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: extrahováno z block_name: 'HC Mladá Boleslav "B" po skončení soutěže ukončila činnost' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -35861,7 +35919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -35975,12 +36033,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0043</t>
+          <t>CLUB_S2001_02_0040</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0042 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: extrahováno z block_name: 'TJ Bohemians Praha ze soutěže před začátkem odstoupila.' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
     </row>
@@ -35995,12 +36053,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0049</t>
+          <t>CLUB_S2001_02_0043</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0042 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -36015,12 +36073,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0056</t>
+          <t>CLUB_S2001_02_0049</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36035,12 +36093,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0065</t>
+          <t>CLUB_S2001_02_0056</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36055,12 +36113,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0066</t>
+          <t>CLUB_S2001_02_0065</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36075,12 +36133,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0067</t>
+          <t>CLUB_S2001_02_0066</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36095,12 +36153,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0069</t>
+          <t>CLUB_S2001_02_0067</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36115,12 +36173,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0096</t>
+          <t>CLUB_S2001_02_0069</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36135,12 +36193,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0105</t>
+          <t>CLUB_S2001_02_0086</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Earth Force Příbram' → 'Příbram' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: extrahováno z block_name: 'HC Mladá Boleslav "B" po skončení soutěže ukončila činnost' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
     </row>
@@ -36155,12 +36213,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0135</t>
+          <t>CLUB_S2001_02_0096</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36175,12 +36233,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0146</t>
+          <t>CLUB_S2001_02_0105</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Earth Force Příbram' → 'Příbram' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36195,12 +36253,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0163</t>
+          <t>CLUB_S2001_02_0135</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36215,12 +36273,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0164</t>
+          <t>CLUB_S2001_02_0146</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36235,7 +36293,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0165</t>
+          <t>CLUB_S2001_02_0163</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -36255,12 +36313,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0211</t>
+          <t>CLUB_S2001_02_0164</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36275,12 +36333,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0225</t>
+          <t>CLUB_S2001_02_0165</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36295,12 +36353,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0227</t>
+          <t>CLUB_S2001_02_0211</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -36315,12 +36373,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0230</t>
+          <t>CLUB_S2001_02_0225</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -36335,12 +36393,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0231</t>
+          <t>CLUB_S2001_02_0227</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36355,7 +36413,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0232</t>
+          <t>CLUB_S2001_02_0230</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -36375,12 +36433,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0236</t>
+          <t>CLUB_S2001_02_0231</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -36395,12 +36453,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0244</t>
+          <t>CLUB_S2001_02_0232</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36415,12 +36473,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0247</t>
+          <t>CLUB_S2001_02_0236</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -36435,12 +36493,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0265</t>
+          <t>CLUB_S2001_02_0244</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36455,12 +36513,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0266</t>
+          <t>CLUB_S2001_02_0247</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -36475,7 +36533,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0268</t>
+          <t>CLUB_S2001_02_0265</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -36495,7 +36553,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0277</t>
+          <t>CLUB_S2001_02_0266</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -36515,12 +36573,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0286</t>
+          <t>CLUB_S2001_02_0268</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36535,12 +36593,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0287</t>
+          <t>CLUB_S2001_02_0277</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36555,12 +36613,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0326</t>
+          <t>CLUB_S2001_02_0286</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -36575,12 +36633,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0333</t>
+          <t>CLUB_S2001_02_0287</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36595,12 +36653,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0338</t>
+          <t>CLUB_S2001_02_0326</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36615,12 +36673,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S2001_02_0355</t>
+          <t>CLUB_S2001_02_0333</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36630,17 +36688,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>pyramida (feeds_into)</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NODE_S2001_02_0030</t>
+          <t>CLUB_S2001_02_0338</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
+          <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36650,17 +36708,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>pyramida (feeds_into)</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NODE_S2001_02_0031</t>
+          <t>CLUB_S2001_02_0355</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
+          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36675,12 +36733,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NODE_S2001_02_0032</t>
+          <t>NODE_S2001_02_0030</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
         </is>
       </c>
     </row>
@@ -36695,17 +36753,57 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>NODE_S2001_02_0031</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0032</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>NODE_S2001_02_0033</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F41"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44005,7 +44103,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Kvalifikace o postup do II.ligy / skupina B / TJ Bohemians Praha ze soutěže před začátkem odstoupila.</t>
+          <t>Kvalifikace o postup do II.ligy / skupina B</t>
         </is>
       </c>
       <c r="C17" s="2" t="n"/>
@@ -46616,7 +46714,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Regionální liga / HC Mladá Boleslav "B" po skončení soutěže ukončila činnost</t>
+          <t>Regionální liga</t>
         </is>
       </c>
       <c r="C13" s="2" t="n"/>

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12379,7 +12379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12979,6 +12979,174 @@
         </is>
       </c>
       <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -35919,7 +36087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -36802,8 +36970,288 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HC Sparta Praha (C)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HC Continental Zlín</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HC IPB Pojišťovna Pardubice</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HC Keramika Plzeň</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HC Vítkovice</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HC Slavia Praha</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HC JME Znojemští Orli</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HC Oceláři Třinec</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HC Vsetín</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HC Becherovka Karlovy Vary</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HC Femax Havířov</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HC České Budějovice</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HC Chemopetrol Litvínov</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HC Vagnerplast Kladno</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -761,13 +761,13 @@
         <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
         <v>196</v>
@@ -777,6 +777,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L5" t="n">
+        <v>132</v>
+      </c>
+      <c r="M5" t="n">
+        <v>103</v>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -833,13 +839,13 @@
         <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
         <v>189</v>
@@ -849,6 +855,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L6" t="n">
+        <v>154</v>
+      </c>
+      <c r="M6" t="n">
+        <v>92</v>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -905,13 +917,13 @@
         <v>52</v>
       </c>
       <c r="G7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
         <v>151</v>
@@ -921,6 +933,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L7" t="n">
+        <v>134</v>
+      </c>
+      <c r="M7" t="n">
+        <v>91</v>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -977,13 +995,13 @@
         <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
         <v>155</v>
@@ -993,6 +1011,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L8" t="n">
+        <v>146</v>
+      </c>
+      <c r="M8" t="n">
+        <v>87</v>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -1049,13 +1073,13 @@
         <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
         <v>158</v>
@@ -1065,6 +1089,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L9" t="n">
+        <v>132</v>
+      </c>
+      <c r="M9" t="n">
+        <v>87</v>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -1121,13 +1151,13 @@
         <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n">
         <v>152</v>
@@ -1137,6 +1167,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L10" t="n">
+        <v>125</v>
+      </c>
+      <c r="M10" t="n">
+        <v>85</v>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -1193,13 +1229,13 @@
         <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H11" t="n">
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J11" t="n">
         <v>153</v>
@@ -1209,6 +1245,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L11" t="n">
+        <v>140</v>
+      </c>
+      <c r="M11" t="n">
+        <v>83</v>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -1265,13 +1307,13 @@
         <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J12" t="n">
         <v>155</v>
@@ -1281,6 +1323,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L12" t="n">
+        <v>165</v>
+      </c>
+      <c r="M12" t="n">
+        <v>79</v>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -1337,13 +1385,13 @@
         <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H13" t="n">
         <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J13" t="n">
         <v>142</v>
@@ -1353,6 +1401,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L13" t="n">
+        <v>162</v>
+      </c>
+      <c r="M13" t="n">
+        <v>67</v>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -1409,13 +1463,13 @@
         <v>52</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H14" t="n">
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
         <v>127</v>
@@ -1425,6 +1479,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L14" t="n">
+        <v>155</v>
+      </c>
+      <c r="M14" t="n">
+        <v>61</v>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -1481,13 +1541,13 @@
         <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J15" t="n">
         <v>161</v>
@@ -1497,6 +1557,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L15" t="n">
+        <v>189</v>
+      </c>
+      <c r="M15" t="n">
+        <v>60</v>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -1553,13 +1619,13 @@
         <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
         <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
         <v>133</v>
@@ -1569,6 +1635,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L16" t="n">
+        <v>155</v>
+      </c>
+      <c r="M16" t="n">
+        <v>59</v>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -1631,7 +1703,7 @@
         <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J17" t="n">
         <v>120</v>
@@ -1641,6 +1713,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L17" t="n">
+        <v>164</v>
+      </c>
+      <c r="M17" t="n">
+        <v>55</v>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>základní část</t>
@@ -1697,13 +1775,13 @@
         <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
         <v>9</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J18" t="n">
         <v>123</v>
@@ -1712,6 +1790,12 @@
         <is>
           <t>:</t>
         </is>
+      </c>
+      <c r="L18" t="n">
+        <v>162</v>
+      </c>
+      <c r="M18" t="n">
+        <v>49</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -12379,7 +12463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12979,174 +13063,6 @@
         </is>
       </c>
       <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -36087,7 +36003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -36970,288 +36886,8 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>HC Sparta Praha (C)</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>HC Continental Zlín</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>HC IPB Pojišťovna Pardubice</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>HC Keramika Plzeň</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>HC Vítkovice</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>HC Slavia Praha</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>HC JME Znojemští Orli</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>HC Oceláři Třinec</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>HC Vsetín</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>HC Becherovka Karlovy Vary</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>HC Femax Havířov</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>HC České Budějovice</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>HC Chemopetrol Litvínov</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>HC Vagnerplast Kladno</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F57"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -13079,7 +13079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13143,6 +13143,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17115,8 +17125,6 @@
         </is>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -17246,7 +17254,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -13331,6 +13331,16 @@
           <t>NODE_S2001_02_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13345,6 +13355,14 @@
         <is>
           <t>NODE_S2000_01_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -13519,6 +13537,16 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13533,6 +13561,14 @@
         <is>
           <t>NODE_S2000_01_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -13613,6 +13649,16 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13627,6 +13673,14 @@
         <is>
           <t>NODE_S2000_01_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -13660,6 +13714,16 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13674,6 +13738,14 @@
         <is>
           <t>NODE_S2000_01_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -13707,6 +13779,8 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13721,6 +13795,14 @@
         <is>
           <t>NODE_S2000_01_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -13754,6 +13836,8 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13768,6 +13852,14 @@
         <is>
           <t>NODE_S2000_01_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -13801,6 +13893,8 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13815,6 +13909,14 @@
         <is>
           <t>NODE_S2000_01_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -13848,6 +13950,8 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13862,6 +13966,14 @@
         <is>
           <t>NODE_S2000_01_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -13895,6 +14007,8 @@
           <t>NODE_S2001_02_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13909,6 +14023,14 @@
         <is>
           <t>NODE_S2000_01_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -13942,6 +14064,8 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13956,6 +14080,14 @@
         <is>
           <t>NODE_S2000_01_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -13989,6 +14121,8 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14003,6 +14137,14 @@
         <is>
           <t>NODE_S2000_01_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -14036,6 +14178,16 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14050,6 +14202,14 @@
         <is>
           <t>NODE_S2000_01_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -14177,6 +14337,16 @@
           <t>NODE_S2001_02_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14191,6 +14361,14 @@
         <is>
           <t>NODE_S2000_01_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -14224,6 +14402,16 @@
           <t>NODE_S2001_02_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14238,6 +14426,14 @@
         <is>
           <t>NODE_S2000_01_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -14271,6 +14467,12 @@
           <t>NODE_S2001_02_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14285,6 +14487,14 @@
         <is>
           <t>NODE_S2000_01_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -14318,6 +14528,12 @@
           <t>NODE_S2001_02_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14332,6 +14548,14 @@
         <is>
           <t>NODE_S2000_01_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -14365,6 +14589,8 @@
           <t>NODE_S2001_02_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14379,6 +14605,14 @@
         <is>
           <t>NODE_S2000_01_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -14412,6 +14646,8 @@
           <t>NODE_S2001_02_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14426,6 +14662,14 @@
         <is>
           <t>NODE_S2000_01_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>6.–14. ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -14859,6 +15103,12 @@
           <t>NODE_S2001_02_0036</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0040</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14868,6 +15118,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -14943,6 +15201,8 @@
           <t>NODE_S2001_02_0036</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14952,6 +15212,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -15126,6 +15394,12 @@
           <t>NODE_S2001_02_0041</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0045</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15140,6 +15414,14 @@
         <is>
           <t>NODE_S2000_01_0039</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -15173,6 +15455,12 @@
           <t>NODE_S2001_02_0041</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0046</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15187,6 +15475,14 @@
         <is>
           <t>NODE_S2000_01_0040</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -15220,6 +15516,8 @@
           <t>NODE_S2001_02_0041</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15234,6 +15532,14 @@
         <is>
           <t>NODE_S2000_01_0041</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -15361,6 +15667,8 @@
           <t>NODE_S2001_02_0041</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15375,6 +15683,14 @@
         <is>
           <t>NODE_S2000_01_0044</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -15450,6 +15766,12 @@
           <t>NODE_S2001_02_0041</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0044</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15459,6 +15781,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -15764,6 +16094,12 @@
           <t>NODE_S2001_02_0056</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0059</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15778,6 +16114,14 @@
         <is>
           <t>NODE_S2000_01_0050</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -15811,6 +16155,12 @@
           <t>NODE_S2001_02_0056</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0060</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15825,6 +16175,14 @@
         <is>
           <t>NODE_S2000_01_0051</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -15858,6 +16216,12 @@
           <t>NODE_S2001_02_0056</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0061</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15872,6 +16236,14 @@
         <is>
           <t>NODE_S2000_01_0052</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -15905,6 +16277,8 @@
           <t>NODE_S2001_02_0056</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15919,6 +16293,14 @@
         <is>
           <t>NODE_S2000_01_0053</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -16187,6 +16569,12 @@
           <t>NODE_S2001_02_0065</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0068</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16201,6 +16589,14 @@
         <is>
           <t>NODE_S2000_01_0062</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -16234,6 +16630,16 @@
           <t>NODE_S2001_02_0065</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0070</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0069</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16243,6 +16649,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -16276,6 +16690,8 @@
           <t>NODE_S2001_02_0065</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16290,6 +16706,14 @@
         <is>
           <t>NODE_S2000_01_0064</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -16323,6 +16747,8 @@
           <t>NODE_S2001_02_0065</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16337,6 +16763,14 @@
         <is>
           <t>NODE_S2000_01_0065</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -16632,6 +17066,8 @@
           <t>NODE_S2001_02_0072</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16641,6 +17077,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -16800,6 +17244,8 @@
           <t>NODE_S2001_02_0072</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16809,6 +17255,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -17030,6 +17484,16 @@
           <t>NODE_S2001_02_0084</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0087</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0088</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17039,6 +17503,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -17072,6 +17544,8 @@
           <t>NODE_S2001_02_0084</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17081,6 +17555,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -17114,6 +17596,8 @@
           <t>NODE_S2001_02_0084</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17124,7 +17608,17 @@
           <t>complete</t>
         </is>
       </c>
-    </row>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>6.–9. ZČ</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90"/>
+    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -17254,6 +17748,7 @@
         </is>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -757,6 +757,11 @@
           <t>HC Sparta Praha (C)</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
@@ -13779,8 +13784,6 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13836,8 +13839,6 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13893,8 +13894,6 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13950,8 +13949,6 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14007,8 +14004,6 @@
           <t>NODE_S2001_02_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14064,8 +14059,6 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14121,8 +14114,6 @@
           <t>NODE_S2001_02_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14472,7 +14463,6 @@
           <t>NODE_S2001_02_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14533,7 +14523,6 @@
           <t>NODE_S2001_02_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14589,8 +14578,6 @@
           <t>NODE_S2001_02_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14646,8 +14633,6 @@
           <t>NODE_S2001_02_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15103,7 +15088,6 @@
           <t>NODE_S2001_02_0036</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>NODE_S2001_02_0040</t>
@@ -15201,8 +15185,6 @@
           <t>NODE_S2001_02_0036</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15399,7 +15381,6 @@
           <t>NODE_S2001_02_0045</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15460,7 +15441,6 @@
           <t>NODE_S2001_02_0046</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15516,8 +15496,6 @@
           <t>NODE_S2001_02_0041</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15667,8 +15645,6 @@
           <t>NODE_S2001_02_0041</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15771,7 +15747,6 @@
           <t>NODE_S2001_02_0044</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16099,7 +16074,6 @@
           <t>NODE_S2001_02_0059</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16160,7 +16134,6 @@
           <t>NODE_S2001_02_0060</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16221,7 +16194,6 @@
           <t>NODE_S2001_02_0061</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16277,8 +16249,6 @@
           <t>NODE_S2001_02_0056</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16574,7 +16544,6 @@
           <t>NODE_S2001_02_0068</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16690,8 +16659,6 @@
           <t>NODE_S2001_02_0065</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16747,8 +16714,6 @@
           <t>NODE_S2001_02_0065</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17066,8 +17031,6 @@
           <t>NODE_S2001_02_0072</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17244,8 +17207,6 @@
           <t>NODE_S2001_02_0072</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17544,8 +17505,6 @@
           <t>NODE_S2001_02_0084</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17596,8 +17555,6 @@
           <t>NODE_S2001_02_0084</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17617,8 +17574,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -17748,7 +17703,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
@@ -36299,7 +36253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36491,6 +36445,18 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HC Sparta Praha</t>
         </is>
       </c>
     </row>

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -17574,6 +17574,8 @@
         <v>2</v>
       </c>
     </row>
+    <row r="90"/>
+    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -17703,6 +17705,7 @@
         </is>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +55,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,6 +117,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21690,8 +21701,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -21821,7 +21830,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
@@ -46560,7 +46568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -46617,7 +46625,7 @@
           <t>CLUB_S2001_02_0008</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46637,7 +46645,7 @@
           <t>CLUB_S2001_02_0018</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46657,7 +46665,7 @@
           <t>CLUB_S2001_02_0020</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46677,7 +46685,7 @@
           <t>CLUB_S2001_02_0040</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: extrahováno z block_name: 'TJ Bohemians Praha ze soutěže před začátkem odstoupila.' [fix_club_notes_in_block_name]</t>
         </is>
@@ -46697,7 +46705,7 @@
           <t>CLUB_S2001_02_0043</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0042 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -46717,7 +46725,7 @@
           <t>CLUB_S2001_02_0049</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -46737,7 +46745,7 @@
           <t>CLUB_S2001_02_0056</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46757,7 +46765,7 @@
           <t>CLUB_S2001_02_0065</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46777,7 +46785,7 @@
           <t>CLUB_S2001_02_0066</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46797,7 +46805,7 @@
           <t>CLUB_S2001_02_0067</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46817,7 +46825,7 @@
           <t>CLUB_S2001_02_0069</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46837,7 +46845,7 @@
           <t>CLUB_S2001_02_0086</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: extrahováno z block_name: 'HC Mladá Boleslav "B" po skončení soutěže ukončila činnost' [fix_club_notes_in_block_name]</t>
         </is>
@@ -46857,7 +46865,7 @@
           <t>CLUB_S2001_02_0096</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46877,7 +46885,7 @@
           <t>CLUB_S2001_02_0105</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Earth Force Příbram' → 'Příbram' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46897,7 +46905,7 @@
           <t>CLUB_S2001_02_0135</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46917,7 +46925,7 @@
           <t>CLUB_S2001_02_0146</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46937,7 +46945,7 @@
           <t>CLUB_S2001_02_0163</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46957,7 +46965,7 @@
           <t>CLUB_S2001_02_0164</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46977,7 +46985,7 @@
           <t>CLUB_S2001_02_0165</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -46997,7 +47005,7 @@
           <t>CLUB_S2001_02_0211</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2000_01_0175 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -47017,7 +47025,7 @@
           <t>CLUB_S2001_02_0225</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -47037,7 +47045,7 @@
           <t>CLUB_S2001_02_0227</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -47057,7 +47065,7 @@
           <t>CLUB_S2001_02_0230</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -47077,7 +47085,7 @@
           <t>CLUB_S2001_02_0231</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -47097,7 +47105,7 @@
           <t>CLUB_S2001_02_0232</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -47117,7 +47125,7 @@
           <t>CLUB_S2001_02_0236</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -47137,7 +47145,7 @@
           <t>CLUB_S2001_02_0244</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -47157,7 +47165,7 @@
           <t>CLUB_S2001_02_0247</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -47177,7 +47185,7 @@
           <t>CLUB_S2001_02_0265</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -47197,7 +47205,7 @@
           <t>CLUB_S2001_02_0266</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -47217,7 +47225,7 @@
           <t>CLUB_S2001_02_0268</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -47237,7 +47245,7 @@
           <t>CLUB_S2001_02_0277</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -47257,7 +47265,7 @@
           <t>CLUB_S2001_02_0286</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -47277,7 +47285,7 @@
           <t>CLUB_S2001_02_0287</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -47297,7 +47305,7 @@
           <t>CLUB_S2001_02_0326</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -47317,7 +47325,7 @@
           <t>CLUB_S2001_02_0333</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -47337,7 +47345,7 @@
           <t>CLUB_S2001_02_0338</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -47357,7 +47365,7 @@
           <t>CLUB_S2001_02_0355</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -47377,7 +47385,7 @@
           <t>NODE_S2001_02_0030</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
         </is>
@@ -47397,7 +47405,7 @@
           <t>NODE_S2001_02_0031</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
         </is>
@@ -47417,7 +47425,7 @@
           <t>NODE_S2001_02_0032</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
@@ -47437,11 +47445,141 @@
           <t>NODE_S2001_02_0033</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>30_Jihočeský L40 Semifinále (Jihočeský kraj) · NODE_S2001_02_0060</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (Spartak Pelhřimov- TJ Lokomotiva Veselí nad Lužnicí 2:0, 2:1), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>30_Severočeský L40 semifinále · NODE_S2001_02_0068</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (HC Draci Bílina – HC Slovan Ústí nad Labem B, Slovan Louny – HC Stadion Litoměřice), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>30_Severočeský L40 O 3.místo · NODE_S2001_02_0069</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (HC Slovan Ústí nad Labem B – Slovan Louny), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>30_Severočeský L40 finále · NODE_S2001_02_0070</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (HC Draci Bílina – HC Stadion Litoměřice), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>30_Jihomoravský L40 (Jihomoravský kraj) · NODE_S2001_02_0082</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (HC Blansko), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F43"/>

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -16595,7 +16598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17195,6 +17198,91 @@
         </is>
       </c>
       <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0060</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (Spartak Pelhřimov- TJ Lokomotiva Veselí nad Lužnicí 2:0, 2:1), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0068</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (HC Draci Bílina – HC Slovan Ústí nad Labem B, Slovan Louny – HC Stadion Litoměřice), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0069</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (HC Slovan Ústí nad Labem B – Slovan Louny), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0070</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (HC Draci Bílina – HC Stadion Litoměřice), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0082</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (HC Blansko), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -47465,7 +47553,7 @@
           <t>30_Jihočeský L40 Semifinále (Jihočeský kraj) · NODE_S2001_02_0060</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>máme jen účastníky (Spartak Pelhřimov- TJ Lokomotiva Veselí nad Lužnicí 2:0, 2:1), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -47491,7 +47579,7 @@
           <t>30_Severočeský L40 semifinále · NODE_S2001_02_0068</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>máme jen účastníky (HC Draci Bílina – HC Slovan Ústí nad Labem B, Slovan Louny – HC Stadion Litoměřice), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -47517,7 +47605,7 @@
           <t>30_Severočeský L40 O 3.místo · NODE_S2001_02_0069</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>máme jen 1 tým (HC Slovan Ústí nad Labem B – Slovan Louny), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -47543,7 +47631,7 @@
           <t>30_Severočeský L40 finále · NODE_S2001_02_0070</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>máme jen účastníky (HC Draci Bílina – HC Stadion Litoměřice), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -47569,7 +47657,7 @@
           <t>30_Jihomoravský L40 (Jihomoravský kraj) · NODE_S2001_02_0082</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>máme jen 1 tým (HC Blansko), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -18974,7 +18974,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KVAL  1.kolo</t>
+          <t>KVAL 1.kolo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -19006,7 +19006,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KVAL  2.kolo</t>
+          <t>KVAL 2.kolo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -19038,7 +19038,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KVAL  skupina A</t>
+          <t>KVAL skupina A</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KVAL  skupina B</t>
+          <t>KVAL skupina B</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -19102,7 +19102,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Praha L40 Pražský přebor</t>
+          <t>Praha, 4. úroveň Pražský přebor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Praha L40 Základní část</t>
+          <t>Praha, 4. úroveň, Základní část</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -19335,7 +19335,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Praha L40 finálová skupina</t>
+          <t>Praha, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_Praha L40 o udržení</t>
+          <t>Praha, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -20036,7 +20036,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Středočeský L50</t>
+          <t>Středočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -20083,7 +20083,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Regionální liga</t>
+          <t>Středočeský, 4. úroveň Regionální liga</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Regionální Soutěž</t>
+          <t>Středočeský, 4. úroveň Regionální Soutěž</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -20214,7 +20214,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50</t>
+          <t>Jihočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -20321,7 +20321,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Čtvrtfinále</t>
+          <t>Jihočeský, 4. úroveň, Čtvrtfinále</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Semifinále</t>
+          <t>Jihočeský, 4. úroveň, Semifinále</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Finále</t>
+          <t>Jihočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Krajská Soutěž</t>
+          <t>Jihočeský, 4. úroveň Krajská Soutěž</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -20543,7 +20543,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Západočeský L40</t>
+          <t>Západočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Západočeský L50</t>
+          <t>Západočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -20637,7 +20637,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Severočeský L40</t>
+          <t>Severočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -20684,7 +20684,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Severočeský L50</t>
+          <t>Severočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -20731,7 +20731,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 základní část</t>
+          <t>Severočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -20791,7 +20791,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 semifinále</t>
+          <t>Severočeský, 4. úroveň, semifinále</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 O 3.místo</t>
+          <t>Severočeský, 4. úroveň O 3.místo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 finále</t>
+          <t>Severočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -20961,7 +20961,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Východočeský L50</t>
+          <t>Východočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -21055,7 +21055,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 Krajská liga</t>
+          <t>Východočeský, 4. úroveň Krajská liga</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -21097,7 +21097,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina Sever</t>
+          <t>Východočeský, 4. úroveň, skupina Sever</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -21139,7 +21139,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina Jih</t>
+          <t>Východočeský, 4. úroveň, skupina Jih</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -21181,7 +21181,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finálová skupina</t>
+          <t>Východočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -21223,7 +21223,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 o udržení</t>
+          <t>Východočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 Krajská 2. liga</t>
+          <t>Východočeský, 4. úroveň Krajská 2. liga</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -21315,7 +21315,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina Jih</t>
+          <t>Východočeský, 4. úroveň, skupina Jih</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -21357,7 +21357,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina Sever:</t>
+          <t>Východočeský, 4. úroveň, skupina Sever:</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -21399,7 +21399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finále</t>
+          <t>Východočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -21496,7 +21496,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50</t>
+          <t>Jihomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -21543,7 +21543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50</t>
+          <t>Severomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -21637,7 +21637,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 základní část</t>
+          <t>Severomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -21697,7 +21697,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 finále</t>
+          <t>Severomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 o udržení</t>
+          <t>Severomoravský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -21789,6 +21789,8 @@
         <v>2</v>
       </c>
     </row>
+    <row r="90"/>
+    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -21821,7 +21823,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -21918,6 +21920,7 @@
         </is>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>

--- a/data/S2001_02_FINAL.xlsx
+++ b/data/S2001_02_FINAL.xlsx
@@ -15182,7 +15182,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -21789,8 +21789,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -21920,7 +21918,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
@@ -47977,7 +47974,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -48052,7 +48049,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -48127,7 +48124,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -48202,7 +48199,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -48277,7 +48274,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -48352,7 +48349,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -48427,7 +48424,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -48502,7 +48499,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -48577,7 +48574,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -48652,7 +48649,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -48727,7 +48724,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -48802,7 +48799,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -48877,7 +48874,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -48952,7 +48949,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -49415,7 +49412,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -49565,7 +49562,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -49756,7 +49753,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -49831,7 +49828,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -50056,7 +50053,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -55617,7 +55614,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -55695,7 +55692,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -55773,7 +55770,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -55851,7 +55848,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -56323,7 +56320,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -56479,7 +56476,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -56557,7 +56554,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
